--- a/output/resultado_impacto_tarifas.xlsx
+++ b/output/resultado_impacto_tarifas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\tarifas_setor_eletrico\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6087E7C5-713E-4CE6-8F5D-9A83D207123D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FBFBC61-EE2F-4225-B38C-4C933C93AB92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1410" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="35">
   <si>
     <t>grupo</t>
   </si>
@@ -70,6 +70,12 @@
     <t>Renda/Gênero/Raça</t>
   </si>
   <si>
+    <t>mulher_negra_renda_alta</t>
+  </si>
+  <si>
+    <t>Mulher negra (renda alta)</t>
+  </si>
+  <si>
     <t>homem_branco_renda_media</t>
   </si>
   <si>
@@ -82,10 +88,28 @@
     <t>Homem branco (renda alta)</t>
   </si>
   <si>
+    <t>mulher_branca_renda_media</t>
+  </si>
+  <si>
+    <t>Mulher branca (renda média)</t>
+  </si>
+  <si>
     <t>mulher_branca_renda_alta</t>
   </si>
   <si>
     <t>Mulher branca (renda alta)</t>
+  </si>
+  <si>
+    <t>homem_negro_renda_alta</t>
+  </si>
+  <si>
+    <t>Homem negro (renda alta)</t>
+  </si>
+  <si>
+    <t>homem_negro_renda_media</t>
+  </si>
+  <si>
+    <t>Homem negro (renda média)</t>
   </si>
   <si>
     <t>rural</t>
@@ -455,25 +479,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.26953125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.6328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.81640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="30.26953125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.6328125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="26.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="27" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.90625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="29.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="26.36328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -514,7 +538,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -554,9 +578,8 @@
       <c r="M2" s="2">
         <v>2.2868324443156571</v>
       </c>
-      <c r="N2" s="3"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -567,38 +590,37 @@
         <v>15</v>
       </c>
       <c r="D3" s="3">
-        <v>1240385910.5073609</v>
+        <v>123128292.87523</v>
       </c>
       <c r="E3" s="2">
-        <v>0.34998012345153062</v>
+        <v>0.15023452904917689</v>
       </c>
       <c r="F3" s="2">
-        <v>0.37022962694636907</v>
+        <v>0.30456679807702819</v>
       </c>
       <c r="G3" s="2">
-        <v>4.0786487550328943</v>
+        <v>5.5578874972937102</v>
       </c>
       <c r="H3" s="2">
-        <v>0.60174974691750549</v>
+        <v>0.26336851167327019</v>
       </c>
       <c r="I3" s="2">
-        <v>0.63656639159736184</v>
+        <v>0.53392056288460688</v>
       </c>
       <c r="J3" s="2">
-        <v>7.0127578443646854</v>
+        <v>9.7432498871852449</v>
       </c>
       <c r="K3" s="2">
-        <v>0.15070040017305941</v>
+        <v>6.3776559285565165E-2</v>
       </c>
       <c r="L3" s="2">
-        <v>0.15941977614756539</v>
+        <v>0.12929266378980109</v>
       </c>
       <c r="M3" s="2">
-        <v>1.7562540223343051</v>
-      </c>
-      <c r="N3" s="3"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+        <v>2.359397295129309</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -609,38 +631,37 @@
         <v>15</v>
       </c>
       <c r="D4" s="3">
-        <v>443984170.67329198</v>
+        <v>1240385910.5073609</v>
       </c>
       <c r="E4" s="2">
-        <v>9.9346272078124964E-2</v>
+        <v>0.34998012345153062</v>
       </c>
       <c r="F4" s="2">
-        <v>0.1613708089606925</v>
+        <v>0.37022962694636907</v>
       </c>
       <c r="G4" s="2">
-        <v>3.6591777853420009</v>
+        <v>4.0786487550328943</v>
       </c>
       <c r="H4" s="2">
-        <v>0.16937366818092109</v>
+        <v>0.60174974691750549</v>
       </c>
       <c r="I4" s="2">
-        <v>0.27511818288965628</v>
+        <v>0.63656639159736184</v>
       </c>
       <c r="J4" s="2">
-        <v>6.238466235976464</v>
+        <v>7.0127578443646854</v>
       </c>
       <c r="K4" s="2">
-        <v>4.3038530357387757E-2</v>
+        <v>0.15070040017305941</v>
       </c>
       <c r="L4" s="2">
-        <v>6.9908636881607117E-2</v>
+        <v>0.15941977614756539</v>
       </c>
       <c r="M4" s="2">
-        <v>1.585219363577884</v>
-      </c>
-      <c r="N4" s="3"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+        <v>1.7562540223343051</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -651,38 +672,37 @@
         <v>15</v>
       </c>
       <c r="D5" s="3">
-        <v>322182091.80313897</v>
+        <v>443984170.67329198</v>
       </c>
       <c r="E5" s="2">
-        <v>9.9994622067301614E-2</v>
+        <v>9.9346272078124964E-2</v>
       </c>
       <c r="F5" s="2">
-        <v>0.1731574714643363</v>
+        <v>0.1613708089606925</v>
       </c>
       <c r="G5" s="2">
-        <v>3.9923212216348838</v>
+        <v>3.6591777853420009</v>
       </c>
       <c r="H5" s="2">
-        <v>0.17165550882387531</v>
+        <v>0.16937366818092109</v>
       </c>
       <c r="I5" s="2">
-        <v>0.2972503246310676</v>
+        <v>0.27511818288965628</v>
       </c>
       <c r="J5" s="2">
-        <v>6.8534078785441714</v>
+        <v>6.238466235976464</v>
       </c>
       <c r="K5" s="2">
-        <v>4.3106811064455089E-2</v>
+        <v>4.3038530357387757E-2</v>
       </c>
       <c r="L5" s="2">
-        <v>7.4646678516251369E-2</v>
+        <v>6.9908636881607117E-2</v>
       </c>
       <c r="M5" s="2">
-        <v>1.7210549232717709</v>
-      </c>
-      <c r="N5" s="3"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+        <v>1.585219363577884</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -690,83 +710,246 @@
         <v>23</v>
       </c>
       <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="3">
+        <v>844471521.53194094</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0.34203807540895942</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.40204854832213999</v>
+      </c>
+      <c r="G6" s="2">
+        <v>4.4433957704740736</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0.59164589997219319</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0.69544998731546326</v>
+      </c>
+      <c r="J6" s="2">
+        <v>7.6860357912243913</v>
+      </c>
+      <c r="K6" s="2">
+        <v>0.14663879138204619</v>
+      </c>
+      <c r="L6" s="2">
+        <v>0.1723665212780007</v>
+      </c>
+      <c r="M6" s="2">
+        <v>1.904975592659842</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="3">
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="3">
+        <v>322182091.80313897</v>
+      </c>
+      <c r="E7" s="2">
+        <v>9.9994622067301614E-2</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.1731574714643363</v>
+      </c>
+      <c r="G7" s="2">
+        <v>3.9923212216348838</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0.17165550882387531</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0.2972503246310676</v>
+      </c>
+      <c r="J7" s="2">
+        <v>6.8534078785441714</v>
+      </c>
+      <c r="K7" s="2">
+        <v>4.3106811064455089E-2</v>
+      </c>
+      <c r="L7" s="2">
+        <v>7.4646678516251369E-2</v>
+      </c>
+      <c r="M7" s="2">
+        <v>1.7210549232717709</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="3">
+        <v>206414355.64383501</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0.12914959941626741</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.24816929292901699</v>
+      </c>
+      <c r="G8" s="2">
+        <v>4.5179537663440197</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0.22364607750018861</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0.42975037607882061</v>
+      </c>
+      <c r="J8" s="2">
+        <v>7.8236606442216559</v>
+      </c>
+      <c r="K8" s="2">
+        <v>5.5324383840874562E-2</v>
+      </c>
+      <c r="L8" s="2">
+        <v>0.10630937518644749</v>
+      </c>
+      <c r="M8" s="2">
+        <v>1.935375792679833</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1621542071.046093</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0.41559506810266988</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.50449460041532634</v>
+      </c>
+      <c r="G9" s="2">
+        <v>5.1378981497238883</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0.7254050296708473</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0.88057570618873049</v>
+      </c>
+      <c r="J9" s="2">
+        <v>8.9680014172485443</v>
+      </c>
+      <c r="K9" s="2">
+        <v>0.17699550497777361</v>
+      </c>
+      <c r="L9" s="2">
+        <v>0.21485643938635851</v>
+      </c>
+      <c r="M9" s="2">
+        <v>2.1881512735134079</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="3">
         <v>946607537.43865001</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E10" s="2">
         <v>0.32276838448721168</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F10" s="2">
         <v>0.5097111108497191</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G10" s="2">
         <v>4.484202301911127</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H10" s="2">
         <v>0.55865488078784309</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I10" s="2">
         <v>0.88221961491172918</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J10" s="2">
         <v>7.7613596089426986</v>
       </c>
-      <c r="K6" s="2">
+      <c r="K10" s="2">
         <v>0.13831584893204141</v>
       </c>
-      <c r="L6" s="2">
+      <c r="L10" s="2">
         <v>0.21842636514502251</v>
       </c>
-      <c r="M6" s="2">
+      <c r="M10" s="2">
         <v>1.9216140055266959</v>
       </c>
-      <c r="N6" s="3"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="3">
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="3">
         <v>5944665833.681695</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E11" s="2">
         <v>0.27285490012309799</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F11" s="2">
         <v>0.36480003437815822</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G11" s="2">
         <v>4.8696514550682402</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H11" s="2">
         <v>0.47474834172090508</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I11" s="2">
         <v>0.63472641064033009</v>
       </c>
-      <c r="J7" s="2">
+      <c r="J11" s="2">
         <v>8.4728511454602717</v>
       </c>
-      <c r="K7" s="2">
+      <c r="K11" s="2">
         <v>0.1164774109240635</v>
       </c>
-      <c r="L7" s="2">
+      <c r="L11" s="2">
         <v>0.15572732426724789</v>
       </c>
-      <c r="M7" s="2">
+      <c r="M11" s="2">
         <v>2.07877664404434</v>
       </c>
-      <c r="N7" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/output/resultado_impacto_tarifas.xlsx
+++ b/output/resultado_impacto_tarifas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\tarifas_setor_eletrico\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FBFBC61-EE2F-4225-B38C-4C933C93AB92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77AB05DC-5AD0-4FD3-887C-80179159AB00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -168,13 +168,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -483,15 +484,15 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="29.90625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.36328125" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="17.453125" customWidth="1"/>
+    <col min="5" max="5" width="29.453125" customWidth="1"/>
+    <col min="6" max="6" width="29.90625" customWidth="1"/>
+    <col min="7" max="7" width="25.1796875" customWidth="1"/>
+    <col min="8" max="8" width="29.453125" customWidth="1"/>
+    <col min="9" max="9" width="29.90625" customWidth="1"/>
+    <col min="10" max="10" width="25.1796875" customWidth="1"/>
     <col min="11" max="11" width="26.36328125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="26.81640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="22.08984375" bestFit="1" customWidth="1"/>
@@ -538,413 +539,413 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+    <row r="2" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D2" s="3">
         <v>1215047642.4342639</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="4">
         <v>0.42527055612603082</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="4">
         <v>0.53677595562657776</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="4">
         <v>5.379918607493253</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="4">
         <v>0.74421428244600973</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="4">
         <v>0.93934632176255839</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="4">
         <v>9.4147412944971904</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2" s="4">
         <v>0.18076899974037189</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2" s="4">
         <v>0.22816640180126341</v>
       </c>
-      <c r="M2" s="2">
+      <c r="M2" s="4">
         <v>2.2868324443156571</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="3" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D3" s="3">
         <v>123128292.87523</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="4">
         <v>0.15023452904917689</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="4">
         <v>0.30456679807702819</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="4">
         <v>5.5578874972937102</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="4">
         <v>0.26336851167327019</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="4">
         <v>0.53392056288460688</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="4">
         <v>9.7432498871852449</v>
       </c>
-      <c r="K3" s="2">
+      <c r="K3" s="4">
         <v>6.3776559285565165E-2</v>
       </c>
-      <c r="L3" s="2">
+      <c r="L3" s="4">
         <v>0.12929266378980109</v>
       </c>
-      <c r="M3" s="2">
+      <c r="M3" s="4">
         <v>2.359397295129309</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+    <row r="4" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D4" s="3">
         <v>1240385910.5073609</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="4">
         <v>0.34998012345153062</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="4">
         <v>0.37022962694636907</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="4">
         <v>4.0786487550328943</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="4">
         <v>0.60174974691750549</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4" s="4">
         <v>0.63656639159736184</v>
       </c>
-      <c r="J4" s="2">
+      <c r="J4" s="4">
         <v>7.0127578443646854</v>
       </c>
-      <c r="K4" s="2">
+      <c r="K4" s="4">
         <v>0.15070040017305941</v>
       </c>
-      <c r="L4" s="2">
+      <c r="L4" s="4">
         <v>0.15941977614756539</v>
       </c>
-      <c r="M4" s="2">
+      <c r="M4" s="4">
         <v>1.7562540223343051</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+    <row r="5" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D5" s="3">
         <v>443984170.67329198</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="4">
         <v>9.9346272078124964E-2</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="4">
         <v>0.1613708089606925</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="4">
         <v>3.6591777853420009</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="4">
         <v>0.16937366818092109</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="4">
         <v>0.27511818288965628</v>
       </c>
-      <c r="J5" s="2">
+      <c r="J5" s="4">
         <v>6.238466235976464</v>
       </c>
-      <c r="K5" s="2">
+      <c r="K5" s="4">
         <v>4.3038530357387757E-2</v>
       </c>
-      <c r="L5" s="2">
+      <c r="L5" s="4">
         <v>6.9908636881607117E-2</v>
       </c>
-      <c r="M5" s="2">
+      <c r="M5" s="4">
         <v>1.585219363577884</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+    <row r="6" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D6" s="3">
         <v>844471521.53194094</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="4">
         <v>0.34203807540895942</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="4">
         <v>0.40204854832213999</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="4">
         <v>4.4433957704740736</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="4">
         <v>0.59164589997219319</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6" s="4">
         <v>0.69544998731546326</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6" s="4">
         <v>7.6860357912243913</v>
       </c>
-      <c r="K6" s="2">
+      <c r="K6" s="4">
         <v>0.14663879138204619</v>
       </c>
-      <c r="L6" s="2">
+      <c r="L6" s="4">
         <v>0.1723665212780007</v>
       </c>
-      <c r="M6" s="2">
+      <c r="M6" s="4">
         <v>1.904975592659842</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+    <row r="7" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="3">
         <v>322182091.80313897</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="4">
         <v>9.9994622067301614E-2</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="4">
         <v>0.1731574714643363</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="4">
         <v>3.9923212216348838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="4">
         <v>0.17165550882387531</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7" s="4">
         <v>0.2972503246310676</v>
       </c>
-      <c r="J7" s="2">
+      <c r="J7" s="4">
         <v>6.8534078785441714</v>
       </c>
-      <c r="K7" s="2">
+      <c r="K7" s="4">
         <v>4.3106811064455089E-2</v>
       </c>
-      <c r="L7" s="2">
+      <c r="L7" s="4">
         <v>7.4646678516251369E-2</v>
       </c>
-      <c r="M7" s="2">
+      <c r="M7" s="4">
         <v>1.7210549232717709</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+    <row r="8" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D8" s="3">
         <v>206414355.64383501</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="4">
         <v>0.12914959941626741</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="4">
         <v>0.24816929292901699</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="4">
         <v>4.5179537663440197</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="4">
         <v>0.22364607750018861</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8" s="4">
         <v>0.42975037607882061</v>
       </c>
-      <c r="J8" s="2">
+      <c r="J8" s="4">
         <v>7.8236606442216559</v>
       </c>
-      <c r="K8" s="2">
+      <c r="K8" s="4">
         <v>5.5324383840874562E-2</v>
       </c>
-      <c r="L8" s="2">
+      <c r="L8" s="4">
         <v>0.10630937518644749</v>
       </c>
-      <c r="M8" s="2">
+      <c r="M8" s="4">
         <v>1.935375792679833</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+    <row r="9" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D9" s="3">
         <v>1621542071.046093</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="4">
         <v>0.41559506810266988</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="4">
         <v>0.50449460041532634</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="4">
         <v>5.1378981497238883</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="4">
         <v>0.7254050296708473</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9" s="4">
         <v>0.88057570618873049</v>
       </c>
-      <c r="J9" s="2">
+      <c r="J9" s="4">
         <v>8.9680014172485443</v>
       </c>
-      <c r="K9" s="2">
+      <c r="K9" s="4">
         <v>0.17699550497777361</v>
       </c>
-      <c r="L9" s="2">
+      <c r="L9" s="4">
         <v>0.21485643938635851</v>
       </c>
-      <c r="M9" s="2">
+      <c r="M9" s="4">
         <v>2.1881512735134079</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+    <row r="10" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="2" t="s">
         <v>32</v>
       </c>
       <c r="D10" s="3">
         <v>946607537.43865001</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="4">
         <v>0.32276838448721168</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="4">
         <v>0.5097111108497191</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="4">
         <v>4.484202301911127</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="4">
         <v>0.55865488078784309</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I10" s="4">
         <v>0.88221961491172918</v>
       </c>
-      <c r="J10" s="2">
+      <c r="J10" s="4">
         <v>7.7613596089426986</v>
       </c>
-      <c r="K10" s="2">
+      <c r="K10" s="4">
         <v>0.13831584893204141</v>
       </c>
-      <c r="L10" s="2">
+      <c r="L10" s="4">
         <v>0.21842636514502251</v>
       </c>
-      <c r="M10" s="2">
+      <c r="M10" s="4">
         <v>1.9216140055266959</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+    <row r="11" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="2" t="s">
         <v>32</v>
       </c>
       <c r="D11" s="3">
         <v>5944665833.681695</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="4">
         <v>0.27285490012309799</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="4">
         <v>0.36480003437815822</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="4">
         <v>4.8696514550682402</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="4">
         <v>0.47474834172090508</v>
       </c>
-      <c r="I11" s="2">
+      <c r="I11" s="4">
         <v>0.63472641064033009</v>
       </c>
-      <c r="J11" s="2">
+      <c r="J11" s="4">
         <v>8.4728511454602717</v>
       </c>
-      <c r="K11" s="2">
+      <c r="K11" s="4">
         <v>0.1164774109240635</v>
       </c>
-      <c r="L11" s="2">
+      <c r="L11" s="4">
         <v>0.15572732426724789</v>
       </c>
-      <c r="M11" s="2">
+      <c r="M11" s="4">
         <v>2.07877664404434</v>
       </c>
     </row>
